--- a/AtchisonRegime/Outputs/Aust/ASX300_Communication/df_regSummary_ASX300_Communication.xlsx
+++ b/AtchisonRegime/Outputs/Aust/ASX300_Communication/df_regSummary_ASX300_Communication.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>1.272571541698505</v>
+        <v>1.131681703508261</v>
       </c>
       <c r="H2" t="n">
-        <v>3.992142625541164</v>
+        <v>4.011759388551176</v>
       </c>
       <c r="I2" t="n">
         <v>-4.724652064266159</v>
@@ -545,19 +545,19 @@
         <v>14.3514762853692</v>
       </c>
       <c r="K2" t="n">
-        <v>41.02564102564102</v>
+        <v>41.77215189873418</v>
       </c>
       <c r="L2" t="n">
         <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>10.66666666666667</v>
+        <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1399415553099277</v>
+        <v>0.1279569235329006</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06473491471119242</v>
+        <v>0.02878101938011102</v>
       </c>
       <c r="P2" t="n">
         <v>0.2858220548416497</v>
@@ -603,7 +603,7 @@
         <v>7.09284827773554</v>
       </c>
       <c r="K3" t="n">
-        <v>8.974358974358974</v>
+        <v>8.860759493670885</v>
       </c>
       <c r="L3" t="n">
         <v>4</v>
@@ -661,7 +661,7 @@
         <v>7.65174934622371</v>
       </c>
       <c r="K4" t="n">
-        <v>6.41025641025641</v>
+        <v>6.329113924050633</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -719,7 +719,7 @@
         <v>8.523880774371349</v>
       </c>
       <c r="K5" t="n">
-        <v>43.58974358974359</v>
+        <v>43.03797468354431</v>
       </c>
       <c r="L5" t="n">
         <v>4</v>
